--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
@@ -6886,7 +6886,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
@@ -6712,7 +6712,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
@@ -6886,7 +6886,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
@@ -6712,7 +6712,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
@@ -6712,7 +6712,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
@@ -6712,7 +6712,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
@@ -6712,7 +6712,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251013_201345.xlsx
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
